--- a/partner_results/Arlanxeo/ClassMissingGermanLabel_Arlanxeo.xlsx
+++ b/partner_results/Arlanxeo/ClassMissingGermanLabel_Arlanxeo.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elongation [Arlanxeo]</t>
+          <t>elastic modulus [Arlanxeo]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +457,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid deformed axially.</t>
+          <t>The component of modulus that is related to energy storage in deformation.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vulcanization [Arlanxeo]</t>
+          <t>moving die rheometer [Arlanxeo]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The process of converting a polymer compound into an elastic network using vulcanization chemicals (e.g. sulfur) and heat (to start the reaction).</t>
+          <t>Generic name for an instrument that applies oscillatory shearing deformation at the vulcanization temperature of a compound at a given time window, using a constant frequency and amplitude.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>butadiene rubber [Arlanxeo]</t>
+          <t>E dash 23 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rubber polymer with butadiene as its only monomer.</t>
+          <t>Elastic modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F Median [Arlanxeo]</t>
+          <t>vinyl content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Median value of tensile strength at break from stress-strain (tensile) measurement</t>
+          <t>Vinyl content is a quality that is based on the vinyl content in polyethylene resins that are determined by the catalyst used for manufacturing the resin.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,22 +526,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
+          <t>solution SBR [Arlanxeo]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mooney Viscosity is a quality of raw and vulcanised polymersbased on the measurement of the torque necessary to rotate a disc in a cylindrical chamber filled with the rubber compound to be vulcanized and is reported in arbitrary Mooney units. It is the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
+          <t>Polymerization is performed in a solution where polymer molecules are dissolved in a solvent (e.g. hexane).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E double dash 60 degree celcius [Arlanxeo]</t>
+          <t>trans content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -553,10 +553,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Trans content is a quality which measures the content of trans isomer in polymers that affect melting points and solubility in polymers.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -564,7 +568,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
+          <t>E dash 0 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -572,14 +576,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius and T = 60 degree celcius for tire compounds.</t>
+          <t>Elastic modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -587,18 +587,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>moving die rheometer [Arlanxeo]</t>
+          <t>E double dash 0 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Generic name for an instrument that applies oscillatory shearing deformation at the vulcanization temperature of a compound at a given time window, using a constant frequency and amplitude.</t>
+          <t>Loss modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -606,18 +606,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>raw polymer [Arlanxeo]</t>
+          <t>carbon black [Arlanxeo]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>polymer</t>
+          <t>filler [Arlanxeo]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Polymer (e.g. BR, SSBR) before being compounded.</t>
+          <t>A filler based on structured carbon which is present in larger fractions in sidewall than in tread compounds. Every CB grade has two major properties that determine its properties.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -625,18 +625,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>elastic modulus [Arlanxeo]</t>
+          <t>gel permeation chromatography method [Arlanxeo]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The component of modulus that is related to energy storage in deformation.</t>
+          <t>The method used to obtain the value of Mw and Mn.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -644,18 +644,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>emulsion SBR [Arlanxeo]</t>
+          <t>cis content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Polymerization is performed in an emulsion where polymer particles (and consequently, crumbs) are carried in a liquid (water) medium.</t>
+          <t>Cis content is a quality in polymers, particularly in polyisoprene, that is crucial for determining the material's properties based on the content of cis isomer which is known for its high elasticity and tensile strength.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -663,7 +667,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LossModulus Gdouble dash(max) [Arlanxeo]</t>
+          <t>mooney stress relaxation [Arlanxeo]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -674,7 +678,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maximum value of loss modulus</t>
+          <t>Mooney stress relaxation is a quality of polymer that refers to the time-dependent process of relaxing a stress applied to a polymer. Due to their structure, polymers do not easily “forget” stress after it is applied to them.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -682,18 +686,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>green compound [Arlanxeo]</t>
+          <t>dynamic mechanical thermal analysis [Arlanxeo]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound that has not been vulcanized and may be heated in an oven to form of network.</t>
+          <t>A method in which the polymer is loaded with (pseudo-) linear, oscillating deformations in a temperature ramp, during which the values of G’ and G” at 3 critical temperatures are read and used .</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -701,18 +705,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>carbon black [Arlanxeo]</t>
+          <t>S100 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A filler based on structured carbon which is present in larger fractions in sidewall than in tread compounds. Every CB grade has two major properties that determine its properties.</t>
+          <t>S100 is a quality of vulcanized compound or polymer which is the stress at deformation value 100.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -720,18 +728,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>silica [Arlanxeo]</t>
+          <t>ramp [Arlanxeo]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A filler that, together with silane, is present only in tread compounds and is used for enforcement.</t>
+          <t>In physical testing, it refers to a constant increase or decrease of testing parameters such as deformation frequency, deformation amplitude or temperature.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -739,18 +747,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E double dash 23 degree celcius [Arlanxeo]</t>
+          <t>vulcanized compound [Arlanxeo]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Compound after being vulcanized. May also be called “vulcanizate”.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -758,7 +766,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E dash 23 degree celcius [Arlanxeo]</t>
+          <t>styrene content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -766,10 +774,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Styrene content is a quality that is a key factor in determining the properties of polymers derived from styrene.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -777,18 +789,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>solution SBR [Arlanxeo]</t>
+          <t>shearing [Arlanxeo]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Polymerization is performed in a solution where polymer molecules are dissolved in a solvent (e.g. hexane).</t>
+          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid are forced to move parallel to each other.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -796,7 +808,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>molecular weight distribution [Arlanxeo]</t>
+          <t>S50 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -804,10 +816,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ratio of Mw to Mn</t>
+          <t>S50 is a quality of vulcanized compound or polymer which is the stress at deformation value 50.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -815,18 +831,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mechanical testing system [Arlanxeo]</t>
+          <t>raw polymer [Arlanxeo]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>polymer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Generic name for an instrument that applies amplitude sweeps to vulcanized rubber to assess the resistance of its network against large deformations.</t>
+          <t>Polymer (e.g. BR, SSBR) before being compounded.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -834,18 +850,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tread [Arlanxeo]</t>
+          <t>elongation [Arlanxeo]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The outer surface of a tire that comes into direct contact with the road.</t>
+          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid deformed axially.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -853,7 +869,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E dash 0 degree celcius [Arlanxeo]</t>
+          <t>LossModulus Gdouble dash(max) [Arlanxeo]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -864,7 +880,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Maximum value of loss modulus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -872,22 +888,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vinyl content [Arlanxeo]</t>
+          <t>emulsion SBR [Arlanxeo]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vinyl content is a quality that is based on the vinyl content in polyethylene resins that are determined by the catalyst used for manufacturing the resin.</t>
+          <t>Polymerization is performed in an emulsion where polymer particles (and consequently, crumbs) are carried in a liquid (water) medium.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -895,7 +907,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>glass transition temperature [Arlanxeo]</t>
+          <t>hardness mean value [Arlanxeo]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -910,7 +922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The glass transition temperature (Tg) is a quality which is a phenomenon of amorphous polymers that is the temperature at which polymers undergo a transition from glassy to rubbery state marking a region of dramatic changes in the physical and mechanical properties.</t>
+          <t>Hardness mean value is a quality of Polymers which indicates the resistance to deformation. Average hardness value measured in Shore A scale.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -918,22 +930,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ML1+4 [Arlanxeo]</t>
+          <t>tread [Arlanxeo]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>surface [dik]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ml1+4 is a quality which is mooney viscosity measured as the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
+          <t>The outer surface of a tire that comes into direct contact with the road.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -941,18 +949,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>inner liner [Arlanxeo]</t>
+          <t>tan d max [Arlanxeo]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The lining of the inner wall of a tire which prevents air from escaping.</t>
+          <t>Maximum loss factor in an amplitude sweep test</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -960,18 +968,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E double dash 0 degree celcius [Arlanxeo]</t>
+          <t>mechanical testing system [Arlanxeo]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Generic name for an instrument that applies amplitude sweeps to vulcanized rubber to assess the resistance of its network against large deformations.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -979,18 +987,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>parts per hundred rubber [Arlanxeo]</t>
+          <t>vulcanization [Arlanxeo]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fraction of rubber compound formulations are not given based on %, so that the sum of all components will be 100%.</t>
+          <t>The process of converting a polymer compound into an elastic network using vulcanization chemicals (e.g. sulfur) and heat (to start the reaction).</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -998,18 +1006,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
+          <t>D Median [Arlanxeo]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Solid particles added to compound to generate enforcement.</t>
+          <t>Median value of elongation from stress-strain (tensile) measurement</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1017,18 +1025,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vulcanized compound [Arlanxeo]</t>
+          <t>S300 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Compound after being vulcanized. May also be called “vulcanizate”.</t>
+          <t>S300 is a quality of vulcanized compound or polymer which is the stress at deformation value 300.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1036,12 +1048,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rebound mean value 1 [Arlanxeo]</t>
+          <t>ML1+4 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
+          <t>mooney viscosity [Arlanxeo]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1051,7 +1063,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rebound mean value  1 is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius.</t>
+          <t>ml1+4 is a quality which is mooney viscosity measured as the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1059,7 +1071,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100 [Arlanxeo]</t>
+          <t>E double dash 23 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1067,14 +1079,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>S100 is a quality of vulcanized compound or polymer which is the stress at deformation value 100.</t>
+          <t>Loss modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1082,22 +1090,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>number averaged molecular weight [Arlanxeo]</t>
+          <t>parts per hundred rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>molecular weight [mi]</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Average molecular weight of the chains of a polymer, calculated by weighing each chain equally, regardless of size (first moment of the molecular weight).</t>
+          <t>Fraction of rubber compound formulations are not given based on %, so that the sum of all components will be 100%.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1105,18 +1109,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>styrene-butadiene rubber [Arlanxeo]</t>
+          <t>molecular weight distribution [Arlanxeo]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>butadiene rubber [Arlanxeo]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rubber polymer with styrene and butadiene as monomers. It is the major component of tread compounds.</t>
+          <t>Ratio of Mw to Mn</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1124,7 +1128,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>weight averaged molecular weight [Arlanxeo]</t>
+          <t>number averaged molecular weight [Arlanxeo]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Average molecular weight of the chains of a polymer, weighted by the mass of each chain (2nd moment of the molecular weight).</t>
+          <t>Average molecular weight of the chains of a polymer, calculated by weighing each chain equally, regardless of size (first moment of the molecular weight).</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1147,18 +1151,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tan d max [Arlanxeo]</t>
+          <t>silica [Arlanxeo]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>filler [Arlanxeo]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Maximum loss factor in an amplitude sweep test</t>
+          <t>A filler that, together with silane, is present only in tread compounds and is used for enforcement.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1166,18 +1170,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D Median [Arlanxeo]</t>
+          <t>E dash 60 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Median value of elongation from stress-strain (tensile) measurement</t>
+          <t>Elastic modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1185,22 +1189,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cis content [Arlanxeo]</t>
+          <t>butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>chemical substance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cis content is a quality in polymers, particularly in polyisoprene, that is crucial for determining the material's properties based on the content of cis isomer which is known for its high elasticity and tensile strength.</t>
+          <t>Rubber polymer with butadiene as its only monomer.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>styrene content [Arlanxeo]</t>
+          <t>rebound mean value [Arlanxeo]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Styrene content is a quality that is a key factor in determining the properties of polymers derived from styrene.</t>
+          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius and T = 60 degree celcius for tire compounds.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1231,18 +1231,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mooney stress relaxation [Arlanxeo]</t>
+          <t>green compound [Arlanxeo]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mooney stress relaxation is a quality of polymer that refers to the time-dependent process of relaxing a stress applied to a polymer. Due to their structure, polymers do not easily “forget” stress after it is applied to them.</t>
+          <t>Compound that has not been vulcanized and may be heated in an oven to form of network.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>trans content [Arlanxeo]</t>
+          <t>loss modulus [Arlanxeo]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1258,14 +1258,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Trans content is a quality which measures the content of trans isomer in polymers that affect melting points and solubility in polymers.</t>
+          <t>The component of modulus that is related to energy loss in deformation.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1273,22 +1269,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S50 [Arlanxeo]</t>
+          <t>silane [Arlanxeo]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>chemical substance</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>S50 is a quality of vulcanized compound or polymer which is the stress at deformation value 50.</t>
+          <t>Silane is necessary to act as intermediary between silica and the SBR matrix, and its role is to enhance the dispersion of silica in the SBR matrix.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1296,22 +1288,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rebound mean value 2 [Arlanxeo]</t>
+          <t>inner liner [Arlanxeo]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>fiat object part</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 60 degree celcius.</t>
+          <t>The lining of the inner wall of a tire which prevents air from escaping.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1319,22 +1307,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ML1+1 [Arlanxeo]</t>
+          <t>filler [Arlanxeo]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ml1+1 is the quality Mooney Viscosity which is the torque at t=1 min. after the start of the Mooney test.</t>
+          <t>Solid particles added to compound to generate enforcement.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1342,18 +1326,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gel permeation chromatography method [Arlanxeo]</t>
+          <t>mooney viscosity [Arlanxeo]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The method used to obtain the value of Mw and Mn.</t>
+          <t>Mooney Viscosity is a quality of raw and vulcanised polymersbased on the measurement of the torque necessary to rotate a disc in a cylindrical chamber filled with the rubber compound to be vulcanized and is reported in arbitrary Mooney units. It is the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1361,7 +1349,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hardness mean value [Arlanxeo]</t>
+          <t>E double dash 60 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1369,14 +1357,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hardness mean value is a quality of Polymers which indicates the resistance to deformation. Average hardness value measured in Shore A scale.</t>
+          <t>Loss modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1384,18 +1368,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>silane [Arlanxeo]</t>
+          <t>styrene-butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Silane is necessary to act as intermediary between silica and the SBR matrix, and its role is to enhance the dispersion of silica in the SBR matrix.</t>
+          <t>Rubber polymer with styrene and butadiene as monomers. It is the major component of tread compounds.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1403,18 +1387,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>loss modulus [Arlanxeo]</t>
+          <t>weight averaged molecular weight [Arlanxeo]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>molecular weight [mi]</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>The component of modulus that is related to energy loss in deformation.</t>
+          <t>Average molecular weight of the chains of a polymer, weighted by the mass of each chain (2nd moment of the molecular weight).</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1422,18 +1410,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>shearing [Arlanxeo]</t>
+          <t>glass transition temperature [Arlanxeo]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid are forced to move parallel to each other.</t>
+          <t>The glass transition temperature (Tg) is a quality which is a phenomenon of amorphous polymers that is the temperature at which polymers undergo a transition from glassy to rubbery state marking a region of dramatic changes in the physical and mechanical properties.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1441,18 +1433,18 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ramp [Arlanxeo]</t>
+          <t>F Median [Arlanxeo]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a constant increase or decrease of testing parameters such as deformation frequency, deformation amplitude or temperature.</t>
+          <t>Median value of tensile strength at break from stress-strain (tensile) measurement</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1460,12 +1452,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S300 [Arlanxeo]</t>
+          <t>ML1+1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>mooney viscosity [Arlanxeo]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1475,7 +1467,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>S300 is a quality of vulcanized compound or polymer which is the stress at deformation value 300.</t>
+          <t>ml1+1 is the quality Mooney Viscosity which is the torque at t=1 min. after the start of the Mooney test.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1483,18 +1475,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>dynamic mechanical thermal analysis [Arlanxeo]</t>
+          <t>rebound mean value 1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>rebound mean value [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A method in which the polymer is loaded with (pseudo-) linear, oscillating deformations in a temperature ramp, during which the values of G’ and G” at 3 critical temperatures are read and used .</t>
+          <t>Rebound mean value  1 is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1502,18 +1498,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E dash 60 degree celcius [Arlanxeo]</t>
+          <t>rebound mean value 2 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>rebound mean value [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 60 degree celcius.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
